--- a/unit4_process/unit4_process.xlsx
+++ b/unit4_process/unit4_process.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1460244-EBB1-411B-9724-8DD2055C370A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD2EAB2-F4BF-432F-9364-7B6AFA0E1A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MucLuc" sheetId="9" r:id="rId1"/>
@@ -10493,16 +10493,28 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10514,22 +10526,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -10553,9 +10553,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>12433</xdr:rowOff>
+      <xdr:colOff>626745</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>172453</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5173185" cy="4027030"/>
     <xdr:pic>
@@ -10579,7 +10579,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11096625" y="18128983"/>
+          <a:off x="10387965" y="439153"/>
           <a:ext cx="5173185" cy="4027030"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -10875,10 +10875,10 @@
       <xdr:rowOff>102139</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>392672</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>1295</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>73212</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -10901,8 +10901,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="657225" y="292639"/>
-          <a:ext cx="10698722" cy="6452356"/>
+          <a:off x="718185" y="277399"/>
+          <a:ext cx="8811447" cy="4477481"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11508,46 +11508,46 @@
   <dimension ref="B2:B16"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="16384" width="8.796875" style="60"/>
+    <col min="1" max="16384" width="8.796875" style="48"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:2">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="49" t="s">
         <v>723</v>
       </c>
     </row>
     <row r="4" spans="2:2">
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="49" t="s">
         <v>724</v>
       </c>
     </row>
     <row r="6" spans="2:2">
-      <c r="B6" s="61" t="s">
+      <c r="B6" s="49" t="s">
         <v>725</v>
       </c>
     </row>
     <row r="8" spans="2:2">
-      <c r="B8" s="61" t="s">
+      <c r="B8" s="49" t="s">
         <v>726</v>
       </c>
     </row>
     <row r="10" spans="2:2">
-      <c r="B10" s="61" t="s">
+      <c r="B10" s="49" t="s">
         <v>727</v>
       </c>
     </row>
     <row r="12" spans="2:2">
-      <c r="B12" s="61" t="s">
+      <c r="B12" s="49" t="s">
         <v>728</v>
       </c>
     </row>
     <row r="14" spans="2:2">
-      <c r="B14" s="62" t="s">
+      <c r="B14" s="50" t="s">
         <v>628</v>
       </c>
     </row>
     <row r="16" spans="2:2">
-      <c r="B16" s="61" t="s">
+      <c r="B16" s="49" t="s">
         <v>729</v>
       </c>
     </row>
@@ -11580,166 +11580,166 @@
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50" t="s">
+      <c r="C2" s="53"/>
+      <c r="D2" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50" t="s">
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49" t="s">
+      <c r="C3" s="51"/>
+      <c r="D3" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49" t="s">
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="49"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="49"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="B4" s="49" t="s">
+      <c r="B4" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="49"/>
-      <c r="D4" s="51" t="s">
+      <c r="C4" s="51"/>
+      <c r="D4" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51" t="s">
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="B5" s="49" t="s">
+      <c r="B5" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49" t="s">
+      <c r="C5" s="51"/>
+      <c r="D5" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49" t="s">
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="51"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="B6" s="49" t="s">
+      <c r="B6" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="49"/>
-      <c r="D6" s="48" t="s">
+      <c r="C6" s="51"/>
+      <c r="D6" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48" t="s">
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="B7" s="49" t="s">
+      <c r="B7" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49" t="s">
+      <c r="C7" s="51"/>
+      <c r="D7" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49" t="s">
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="49"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="51"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="B8" s="49" t="s">
+      <c r="B8" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49" t="s">
+      <c r="C8" s="51"/>
+      <c r="D8" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49" t="s">
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49"/>
-      <c r="K8" s="49"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="B9" s="49" t="s">
+      <c r="B9" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="49"/>
-      <c r="D9" s="48" t="s">
+      <c r="C9" s="51"/>
+      <c r="D9" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48" t="s">
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="48"/>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="52"/>
+      <c r="K9" s="52"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="B10" s="49" t="s">
+      <c r="B10" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49" t="s">
+      <c r="C10" s="51"/>
+      <c r="D10" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49" t="s">
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="51"/>
     </row>
     <row r="12" spans="1:11" ht="22.8">
       <c r="A12" s="5" t="s">
@@ -11752,40 +11752,40 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="30" customHeight="1">
-      <c r="B16" s="50" t="s">
+      <c r="B16" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50" t="s">
+      <c r="C16" s="53"/>
+      <c r="D16" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="53"/>
     </row>
     <row r="17" spans="1:26">
-      <c r="B17" s="48" t="s">
+      <c r="B17" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="48"/>
-      <c r="D17" s="49" t="s">
+      <c r="C17" s="52"/>
+      <c r="D17" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="49"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
     </row>
     <row r="18" spans="1:26">
-      <c r="B18" s="48" t="s">
+      <c r="B18" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="48"/>
-      <c r="D18" s="49" t="s">
+      <c r="C18" s="52"/>
+      <c r="D18" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="49"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
     </row>
     <row r="22" spans="1:26" ht="21">
       <c r="A22" s="10" t="s">
@@ -11861,14 +11861,14 @@
       <c r="C29" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D29" s="52" t="s">
+      <c r="D29" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="E29" s="53"/>
-      <c r="F29" s="53"/>
-      <c r="G29" s="53"/>
-      <c r="H29" s="53"/>
-      <c r="I29" s="54"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="60"/>
       <c r="O29" s="22"/>
       <c r="Q29" s="12" t="s">
         <v>162</v>
@@ -11996,17 +11996,17 @@
       <c r="P37" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Q37" s="50" t="s">
+      <c r="Q37" s="53" t="s">
         <v>170</v>
       </c>
-      <c r="R37" s="50"/>
-      <c r="S37" s="50"/>
-      <c r="T37" s="50"/>
-      <c r="U37" s="50"/>
-      <c r="V37" s="50"/>
-      <c r="W37" s="50"/>
-      <c r="X37" s="50"/>
-      <c r="Y37" s="50"/>
+      <c r="R37" s="53"/>
+      <c r="S37" s="53"/>
+      <c r="T37" s="53"/>
+      <c r="U37" s="53"/>
+      <c r="V37" s="53"/>
+      <c r="W37" s="53"/>
+      <c r="X37" s="53"/>
+      <c r="Y37" s="53"/>
       <c r="Z37" s="23"/>
     </row>
     <row r="38" spans="2:26">
@@ -12017,17 +12017,17 @@
       <c r="P38" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="Q38" s="49" t="s">
+      <c r="Q38" s="51" t="s">
         <v>172</v>
       </c>
-      <c r="R38" s="49"/>
-      <c r="S38" s="49"/>
-      <c r="T38" s="49"/>
-      <c r="U38" s="49"/>
-      <c r="V38" s="49"/>
-      <c r="W38" s="49"/>
-      <c r="X38" s="49"/>
-      <c r="Y38" s="49"/>
+      <c r="R38" s="51"/>
+      <c r="S38" s="51"/>
+      <c r="T38" s="51"/>
+      <c r="U38" s="51"/>
+      <c r="V38" s="51"/>
+      <c r="W38" s="51"/>
+      <c r="X38" s="51"/>
+      <c r="Y38" s="51"/>
       <c r="Z38" s="23"/>
     </row>
     <row r="39" spans="2:26">
@@ -12038,17 +12038,17 @@
       <c r="P39" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="Q39" s="51" t="s">
+      <c r="Q39" s="54" t="s">
         <v>174</v>
       </c>
-      <c r="R39" s="51"/>
-      <c r="S39" s="51"/>
-      <c r="T39" s="51"/>
-      <c r="U39" s="51"/>
-      <c r="V39" s="51"/>
-      <c r="W39" s="51"/>
-      <c r="X39" s="51"/>
-      <c r="Y39" s="51"/>
+      <c r="R39" s="54"/>
+      <c r="S39" s="54"/>
+      <c r="T39" s="54"/>
+      <c r="U39" s="54"/>
+      <c r="V39" s="54"/>
+      <c r="W39" s="54"/>
+      <c r="X39" s="54"/>
+      <c r="Y39" s="54"/>
       <c r="Z39" s="23"/>
     </row>
     <row r="40" spans="2:26" ht="26.4">
@@ -12059,17 +12059,17 @@
       <c r="P40" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="Q40" s="49" t="s">
+      <c r="Q40" s="51" t="s">
         <v>176</v>
       </c>
-      <c r="R40" s="49"/>
-      <c r="S40" s="49"/>
-      <c r="T40" s="49"/>
-      <c r="U40" s="49"/>
-      <c r="V40" s="49"/>
-      <c r="W40" s="49"/>
-      <c r="X40" s="49"/>
-      <c r="Y40" s="49"/>
+      <c r="R40" s="51"/>
+      <c r="S40" s="51"/>
+      <c r="T40" s="51"/>
+      <c r="U40" s="51"/>
+      <c r="V40" s="51"/>
+      <c r="W40" s="51"/>
+      <c r="X40" s="51"/>
+      <c r="Y40" s="51"/>
       <c r="Z40" s="23"/>
     </row>
     <row r="41" spans="2:26">
@@ -12205,14 +12205,14 @@
       <c r="C55" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D55" s="50" t="s">
+      <c r="D55" s="53" t="s">
         <v>131</v>
       </c>
-      <c r="E55" s="50"/>
-      <c r="F55" s="50"/>
-      <c r="G55" s="50"/>
-      <c r="H55" s="50"/>
-      <c r="I55" s="50"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="53"/>
+      <c r="G55" s="53"/>
+      <c r="H55" s="53"/>
+      <c r="I55" s="53"/>
       <c r="O55" s="22"/>
       <c r="Q55" s="12" t="s">
         <v>186</v>
@@ -12223,14 +12223,14 @@
       <c r="C56" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D56" s="49" t="s">
+      <c r="D56" s="51" t="s">
         <v>133</v>
       </c>
-      <c r="E56" s="49"/>
-      <c r="F56" s="49"/>
-      <c r="G56" s="49"/>
-      <c r="H56" s="49"/>
-      <c r="I56" s="49"/>
+      <c r="E56" s="51"/>
+      <c r="F56" s="51"/>
+      <c r="G56" s="51"/>
+      <c r="H56" s="51"/>
+      <c r="I56" s="51"/>
       <c r="O56" s="22"/>
       <c r="P56" s="5" t="s">
         <v>187</v>
@@ -12241,14 +12241,14 @@
       <c r="C57" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D57" s="49" t="s">
+      <c r="D57" s="51" t="s">
         <v>135</v>
       </c>
-      <c r="E57" s="49"/>
-      <c r="F57" s="49"/>
-      <c r="G57" s="49"/>
-      <c r="H57" s="49"/>
-      <c r="I57" s="49"/>
+      <c r="E57" s="51"/>
+      <c r="F57" s="51"/>
+      <c r="G57" s="51"/>
+      <c r="H57" s="51"/>
+      <c r="I57" s="51"/>
       <c r="O57" s="22"/>
       <c r="Q57" s="13" t="s">
         <v>188</v>
@@ -12259,14 +12259,14 @@
       <c r="C58" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D58" s="49" t="s">
+      <c r="D58" s="51" t="s">
         <v>137</v>
       </c>
-      <c r="E58" s="49"/>
-      <c r="F58" s="49"/>
-      <c r="G58" s="49"/>
-      <c r="H58" s="49"/>
-      <c r="I58" s="49"/>
+      <c r="E58" s="51"/>
+      <c r="F58" s="51"/>
+      <c r="G58" s="51"/>
+      <c r="H58" s="51"/>
+      <c r="I58" s="51"/>
       <c r="O58" s="22"/>
       <c r="Q58" s="13" t="s">
         <v>189</v>
@@ -12381,45 +12381,45 @@
       <c r="C79" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D79" s="50" t="s">
+      <c r="D79" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="E79" s="50"/>
-      <c r="F79" s="50"/>
-      <c r="G79" s="50"/>
+      <c r="E79" s="53"/>
+      <c r="F79" s="53"/>
+      <c r="G79" s="53"/>
     </row>
     <row r="80" spans="2:16">
       <c r="C80" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D80" s="48" t="s">
+      <c r="D80" s="52" t="s">
         <v>151</v>
       </c>
-      <c r="E80" s="48"/>
-      <c r="F80" s="48"/>
-      <c r="G80" s="48"/>
+      <c r="E80" s="52"/>
+      <c r="F80" s="52"/>
+      <c r="G80" s="52"/>
     </row>
     <row r="81" spans="1:7">
       <c r="C81" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D81" s="48" t="s">
+      <c r="D81" s="52" t="s">
         <v>153</v>
       </c>
-      <c r="E81" s="48"/>
-      <c r="F81" s="48"/>
-      <c r="G81" s="48"/>
+      <c r="E81" s="52"/>
+      <c r="F81" s="52"/>
+      <c r="G81" s="52"/>
     </row>
     <row r="82" spans="1:7">
       <c r="C82" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="D82" s="49" t="s">
+      <c r="D82" s="51" t="s">
         <v>155</v>
       </c>
-      <c r="E82" s="49"/>
-      <c r="F82" s="49"/>
-      <c r="G82" s="49"/>
+      <c r="E82" s="51"/>
+      <c r="F82" s="51"/>
+      <c r="G82" s="51"/>
     </row>
     <row r="83" spans="1:7">
       <c r="C83" s="35"/>
@@ -12874,17 +12874,31 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="H10:K10"/>
-    <mergeCell ref="D9:G9"/>
-    <mergeCell ref="D10:G10"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="H3:K3"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="H5:K5"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="H8:K8"/>
-    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="D80:G80"/>
+    <mergeCell ref="D81:G81"/>
+    <mergeCell ref="D82:G82"/>
+    <mergeCell ref="Q37:Y37"/>
+    <mergeCell ref="Q38:Y38"/>
+    <mergeCell ref="Q39:Y39"/>
+    <mergeCell ref="Q40:Y40"/>
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="D56:I56"/>
+    <mergeCell ref="D57:I57"/>
+    <mergeCell ref="D58:I58"/>
+    <mergeCell ref="D79:G79"/>
+    <mergeCell ref="D34:I34"/>
+    <mergeCell ref="D35:I35"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="D29:I29"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="D32:I32"/>
+    <mergeCell ref="D33:I33"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B10:C10"/>
@@ -12901,31 +12915,17 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D34:I34"/>
-    <mergeCell ref="D35:I35"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="D29:I29"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="D32:I32"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D80:G80"/>
-    <mergeCell ref="D81:G81"/>
-    <mergeCell ref="D82:G82"/>
-    <mergeCell ref="Q37:Y37"/>
-    <mergeCell ref="Q38:Y38"/>
-    <mergeCell ref="Q39:Y39"/>
-    <mergeCell ref="Q40:Y40"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="D56:I56"/>
-    <mergeCell ref="D57:I57"/>
-    <mergeCell ref="D58:I58"/>
-    <mergeCell ref="D79:G79"/>
+    <mergeCell ref="H10:K10"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="D10:G10"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="H5:K5"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="H8:K8"/>
+    <mergeCell ref="H9:K9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -13614,127 +13614,127 @@
       <c r="C81" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D81" s="50" t="s">
+      <c r="D81" s="53" t="s">
         <v>419</v>
       </c>
-      <c r="E81" s="50"/>
-      <c r="F81" s="50" t="s">
+      <c r="E81" s="53"/>
+      <c r="F81" s="53" t="s">
         <v>420</v>
       </c>
-      <c r="G81" s="50"/>
-      <c r="H81" s="50"/>
-      <c r="I81" s="50" t="s">
+      <c r="G81" s="53"/>
+      <c r="H81" s="53"/>
+      <c r="I81" s="53" t="s">
         <v>421</v>
       </c>
-      <c r="J81" s="50"/>
+      <c r="J81" s="53"/>
     </row>
     <row r="82" spans="1:10">
       <c r="C82" s="18" t="s">
         <v>422</v>
       </c>
-      <c r="D82" s="58" t="s">
+      <c r="D82" s="61" t="s">
         <v>423</v>
       </c>
-      <c r="E82" s="58"/>
-      <c r="F82" s="58" t="s">
+      <c r="E82" s="61"/>
+      <c r="F82" s="61" t="s">
         <v>424</v>
       </c>
-      <c r="G82" s="58"/>
-      <c r="H82" s="58"/>
-      <c r="I82" s="58" t="s">
+      <c r="G82" s="61"/>
+      <c r="H82" s="61"/>
+      <c r="I82" s="61" t="s">
         <v>423</v>
       </c>
-      <c r="J82" s="58"/>
+      <c r="J82" s="61"/>
     </row>
     <row r="83" spans="1:10" ht="30" customHeight="1">
       <c r="C83" s="18" t="s">
         <v>425</v>
       </c>
-      <c r="D83" s="58" t="s">
+      <c r="D83" s="61" t="s">
         <v>423</v>
       </c>
-      <c r="E83" s="58"/>
-      <c r="F83" s="58" t="s">
+      <c r="E83" s="61"/>
+      <c r="F83" s="61" t="s">
         <v>426</v>
       </c>
-      <c r="G83" s="58"/>
-      <c r="H83" s="58"/>
-      <c r="I83" s="58" t="s">
+      <c r="G83" s="61"/>
+      <c r="H83" s="61"/>
+      <c r="I83" s="61" t="s">
         <v>423</v>
       </c>
-      <c r="J83" s="58"/>
+      <c r="J83" s="61"/>
     </row>
     <row r="84" spans="1:10">
       <c r="C84" s="18" t="s">
         <v>427</v>
       </c>
-      <c r="D84" s="58" t="s">
+      <c r="D84" s="61" t="s">
         <v>424</v>
       </c>
-      <c r="E84" s="58"/>
-      <c r="F84" s="58" t="s">
+      <c r="E84" s="61"/>
+      <c r="F84" s="61" t="s">
         <v>424</v>
       </c>
-      <c r="G84" s="58"/>
-      <c r="H84" s="58"/>
-      <c r="I84" s="58" t="s">
+      <c r="G84" s="61"/>
+      <c r="H84" s="61"/>
+      <c r="I84" s="61" t="s">
         <v>423</v>
       </c>
-      <c r="J84" s="58"/>
+      <c r="J84" s="61"/>
     </row>
     <row r="85" spans="1:10" ht="30" customHeight="1">
       <c r="C85" s="18" t="s">
         <v>428</v>
       </c>
-      <c r="D85" s="58" t="s">
+      <c r="D85" s="61" t="s">
         <v>424</v>
       </c>
-      <c r="E85" s="58"/>
-      <c r="F85" s="58" t="s">
+      <c r="E85" s="61"/>
+      <c r="F85" s="61" t="s">
         <v>426</v>
       </c>
-      <c r="G85" s="58"/>
-      <c r="H85" s="58"/>
-      <c r="I85" s="58" t="s">
+      <c r="G85" s="61"/>
+      <c r="H85" s="61"/>
+      <c r="I85" s="61" t="s">
         <v>423</v>
       </c>
-      <c r="J85" s="58"/>
+      <c r="J85" s="61"/>
     </row>
     <row r="86" spans="1:10">
       <c r="C86" s="18" t="s">
         <v>429</v>
       </c>
-      <c r="D86" s="58" t="s">
+      <c r="D86" s="61" t="s">
         <v>423</v>
       </c>
-      <c r="E86" s="58"/>
-      <c r="F86" s="58" t="s">
+      <c r="E86" s="61"/>
+      <c r="F86" s="61" t="s">
         <v>424</v>
       </c>
-      <c r="G86" s="58"/>
-      <c r="H86" s="58"/>
-      <c r="I86" s="58" t="s">
+      <c r="G86" s="61"/>
+      <c r="H86" s="61"/>
+      <c r="I86" s="61" t="s">
         <v>424</v>
       </c>
-      <c r="J86" s="58"/>
+      <c r="J86" s="61"/>
     </row>
     <row r="87" spans="1:10" ht="30" customHeight="1">
       <c r="C87" s="18" t="s">
         <v>430</v>
       </c>
-      <c r="D87" s="58" t="s">
+      <c r="D87" s="61" t="s">
         <v>423</v>
       </c>
-      <c r="E87" s="58"/>
-      <c r="F87" s="58" t="s">
+      <c r="E87" s="61"/>
+      <c r="F87" s="61" t="s">
         <v>426</v>
       </c>
-      <c r="G87" s="58"/>
-      <c r="H87" s="58"/>
-      <c r="I87" s="58" t="s">
+      <c r="G87" s="61"/>
+      <c r="H87" s="61"/>
+      <c r="I87" s="61" t="s">
         <v>424</v>
       </c>
-      <c r="J87" s="58"/>
+      <c r="J87" s="61"/>
     </row>
     <row r="90" spans="1:10" ht="21">
       <c r="A90" s="10" t="s">
@@ -13798,45 +13798,45 @@
       <c r="C105" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D105" s="50" t="s">
+      <c r="D105" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="E105" s="50"/>
-      <c r="F105" s="50"/>
-      <c r="G105" s="50"/>
+      <c r="E105" s="53"/>
+      <c r="F105" s="53"/>
+      <c r="G105" s="53"/>
     </row>
     <row r="106" spans="2:7">
       <c r="C106" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="D106" s="49" t="s">
+      <c r="D106" s="51" t="s">
         <v>468</v>
       </c>
-      <c r="E106" s="49"/>
-      <c r="F106" s="49"/>
-      <c r="G106" s="49"/>
+      <c r="E106" s="51"/>
+      <c r="F106" s="51"/>
+      <c r="G106" s="51"/>
     </row>
     <row r="107" spans="2:7" ht="27.6">
       <c r="C107" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="D107" s="49" t="s">
+      <c r="D107" s="51" t="s">
         <v>470</v>
       </c>
-      <c r="E107" s="49"/>
-      <c r="F107" s="49"/>
-      <c r="G107" s="49"/>
+      <c r="E107" s="51"/>
+      <c r="F107" s="51"/>
+      <c r="G107" s="51"/>
     </row>
     <row r="108" spans="2:7" ht="27.6">
       <c r="C108" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="D108" s="49" t="s">
+      <c r="D108" s="51" t="s">
         <v>472</v>
       </c>
-      <c r="E108" s="49"/>
-      <c r="F108" s="49"/>
-      <c r="G108" s="49"/>
+      <c r="E108" s="51"/>
+      <c r="F108" s="51"/>
+      <c r="G108" s="51"/>
     </row>
     <row r="110" spans="2:7" ht="30">
       <c r="B110" s="32" t="s">
@@ -13902,95 +13902,95 @@
       </c>
     </row>
     <row r="125" spans="2:9">
-      <c r="C125" s="50" t="s">
+      <c r="C125" s="53" t="s">
         <v>483</v>
       </c>
-      <c r="D125" s="50"/>
-      <c r="E125" s="50" t="s">
+      <c r="D125" s="53"/>
+      <c r="E125" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="F125" s="50"/>
-      <c r="G125" s="50"/>
-      <c r="H125" s="50"/>
-      <c r="I125" s="50"/>
+      <c r="F125" s="53"/>
+      <c r="G125" s="53"/>
+      <c r="H125" s="53"/>
+      <c r="I125" s="53"/>
     </row>
     <row r="126" spans="2:9">
-      <c r="C126" s="48" t="s">
+      <c r="C126" s="52" t="s">
         <v>484</v>
       </c>
-      <c r="D126" s="48"/>
-      <c r="E126" s="49" t="s">
+      <c r="D126" s="52"/>
+      <c r="E126" s="51" t="s">
         <v>485</v>
       </c>
-      <c r="F126" s="49"/>
-      <c r="G126" s="49"/>
-      <c r="H126" s="49"/>
-      <c r="I126" s="49"/>
+      <c r="F126" s="51"/>
+      <c r="G126" s="51"/>
+      <c r="H126" s="51"/>
+      <c r="I126" s="51"/>
     </row>
     <row r="127" spans="2:9" ht="25.5" customHeight="1">
-      <c r="C127" s="48" t="s">
+      <c r="C127" s="52" t="s">
         <v>486</v>
       </c>
-      <c r="D127" s="48"/>
-      <c r="E127" s="49" t="s">
+      <c r="D127" s="52"/>
+      <c r="E127" s="51" t="s">
         <v>487</v>
       </c>
-      <c r="F127" s="49"/>
-      <c r="G127" s="49"/>
-      <c r="H127" s="49"/>
-      <c r="I127" s="49"/>
+      <c r="F127" s="51"/>
+      <c r="G127" s="51"/>
+      <c r="H127" s="51"/>
+      <c r="I127" s="51"/>
     </row>
     <row r="128" spans="2:9">
-      <c r="C128" s="48" t="s">
+      <c r="C128" s="52" t="s">
         <v>488</v>
       </c>
-      <c r="D128" s="48"/>
-      <c r="E128" s="49" t="s">
+      <c r="D128" s="52"/>
+      <c r="E128" s="51" t="s">
         <v>489</v>
       </c>
-      <c r="F128" s="49"/>
-      <c r="G128" s="49"/>
-      <c r="H128" s="49"/>
-      <c r="I128" s="49"/>
+      <c r="F128" s="51"/>
+      <c r="G128" s="51"/>
+      <c r="H128" s="51"/>
+      <c r="I128" s="51"/>
     </row>
     <row r="129" spans="2:9">
-      <c r="C129" s="48" t="s">
+      <c r="C129" s="52" t="s">
         <v>490</v>
       </c>
-      <c r="D129" s="48"/>
-      <c r="E129" s="49" t="s">
+      <c r="D129" s="52"/>
+      <c r="E129" s="51" t="s">
         <v>491</v>
       </c>
-      <c r="F129" s="49"/>
-      <c r="G129" s="49"/>
-      <c r="H129" s="49"/>
-      <c r="I129" s="49"/>
+      <c r="F129" s="51"/>
+      <c r="G129" s="51"/>
+      <c r="H129" s="51"/>
+      <c r="I129" s="51"/>
     </row>
     <row r="130" spans="2:9">
-      <c r="C130" s="48" t="s">
+      <c r="C130" s="52" t="s">
         <v>492</v>
       </c>
-      <c r="D130" s="48"/>
-      <c r="E130" s="49" t="s">
+      <c r="D130" s="52"/>
+      <c r="E130" s="51" t="s">
         <v>493</v>
       </c>
-      <c r="F130" s="49"/>
-      <c r="G130" s="49"/>
-      <c r="H130" s="49"/>
-      <c r="I130" s="49"/>
+      <c r="F130" s="51"/>
+      <c r="G130" s="51"/>
+      <c r="H130" s="51"/>
+      <c r="I130" s="51"/>
     </row>
     <row r="131" spans="2:9">
-      <c r="C131" s="48" t="s">
+      <c r="C131" s="52" t="s">
         <v>494</v>
       </c>
-      <c r="D131" s="48"/>
-      <c r="E131" s="49" t="s">
+      <c r="D131" s="52"/>
+      <c r="E131" s="51" t="s">
         <v>495</v>
       </c>
-      <c r="F131" s="49"/>
-      <c r="G131" s="49"/>
-      <c r="H131" s="49"/>
-      <c r="I131" s="49"/>
+      <c r="F131" s="51"/>
+      <c r="G131" s="51"/>
+      <c r="H131" s="51"/>
+      <c r="I131" s="51"/>
     </row>
     <row r="135" spans="2:9" ht="30">
       <c r="B135" s="32" t="s">
@@ -13998,69 +13998,69 @@
       </c>
     </row>
     <row r="137" spans="2:9">
-      <c r="C137" s="50" t="s">
+      <c r="C137" s="53" t="s">
         <v>192</v>
       </c>
-      <c r="D137" s="50"/>
-      <c r="E137" s="50" t="s">
+      <c r="D137" s="53"/>
+      <c r="E137" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="F137" s="50"/>
-      <c r="G137" s="50"/>
-      <c r="H137" s="50"/>
-      <c r="I137" s="50"/>
+      <c r="F137" s="53"/>
+      <c r="G137" s="53"/>
+      <c r="H137" s="53"/>
+      <c r="I137" s="53"/>
     </row>
     <row r="138" spans="2:9">
-      <c r="C138" s="49" t="s">
+      <c r="C138" s="51" t="s">
         <v>497</v>
       </c>
-      <c r="D138" s="49"/>
-      <c r="E138" s="49" t="s">
+      <c r="D138" s="51"/>
+      <c r="E138" s="51" t="s">
         <v>498</v>
       </c>
-      <c r="F138" s="49"/>
-      <c r="G138" s="49"/>
-      <c r="H138" s="49"/>
-      <c r="I138" s="49"/>
+      <c r="F138" s="51"/>
+      <c r="G138" s="51"/>
+      <c r="H138" s="51"/>
+      <c r="I138" s="51"/>
     </row>
     <row r="139" spans="2:9">
-      <c r="C139" s="49" t="s">
+      <c r="C139" s="51" t="s">
         <v>499</v>
       </c>
-      <c r="D139" s="49"/>
-      <c r="E139" s="49" t="s">
+      <c r="D139" s="51"/>
+      <c r="E139" s="51" t="s">
         <v>500</v>
       </c>
-      <c r="F139" s="49"/>
-      <c r="G139" s="49"/>
-      <c r="H139" s="49"/>
-      <c r="I139" s="49"/>
+      <c r="F139" s="51"/>
+      <c r="G139" s="51"/>
+      <c r="H139" s="51"/>
+      <c r="I139" s="51"/>
     </row>
     <row r="140" spans="2:9">
-      <c r="C140" s="49" t="s">
+      <c r="C140" s="51" t="s">
         <v>501</v>
       </c>
-      <c r="D140" s="49"/>
-      <c r="E140" s="49" t="s">
+      <c r="D140" s="51"/>
+      <c r="E140" s="51" t="s">
         <v>502</v>
       </c>
-      <c r="F140" s="49"/>
-      <c r="G140" s="49"/>
-      <c r="H140" s="49"/>
-      <c r="I140" s="49"/>
+      <c r="F140" s="51"/>
+      <c r="G140" s="51"/>
+      <c r="H140" s="51"/>
+      <c r="I140" s="51"/>
     </row>
     <row r="141" spans="2:9">
-      <c r="C141" s="49" t="s">
+      <c r="C141" s="51" t="s">
         <v>503</v>
       </c>
-      <c r="D141" s="49"/>
-      <c r="E141" s="49" t="s">
+      <c r="D141" s="51"/>
+      <c r="E141" s="51" t="s">
         <v>504</v>
       </c>
-      <c r="F141" s="49"/>
-      <c r="G141" s="49"/>
-      <c r="H141" s="49"/>
-      <c r="I141" s="49"/>
+      <c r="F141" s="51"/>
+      <c r="G141" s="51"/>
+      <c r="H141" s="51"/>
+      <c r="I141" s="51"/>
     </row>
     <row r="143" spans="2:9" ht="30">
       <c r="B143" s="32" t="s">
@@ -14174,43 +14174,43 @@
       </c>
     </row>
     <row r="180" spans="2:9">
-      <c r="C180" s="50" t="s">
+      <c r="C180" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="D180" s="50"/>
-      <c r="E180" s="50"/>
-      <c r="F180" s="50" t="s">
+      <c r="D180" s="53"/>
+      <c r="E180" s="53"/>
+      <c r="F180" s="53" t="s">
         <v>514</v>
       </c>
-      <c r="G180" s="50"/>
-      <c r="H180" s="50"/>
-      <c r="I180" s="50"/>
+      <c r="G180" s="53"/>
+      <c r="H180" s="53"/>
+      <c r="I180" s="53"/>
     </row>
     <row r="181" spans="2:9" ht="26.25" customHeight="1">
-      <c r="C181" s="48" t="s">
+      <c r="C181" s="52" t="s">
         <v>515</v>
       </c>
-      <c r="D181" s="48"/>
-      <c r="E181" s="48"/>
-      <c r="F181" s="49" t="s">
+      <c r="D181" s="52"/>
+      <c r="E181" s="52"/>
+      <c r="F181" s="51" t="s">
         <v>516</v>
       </c>
-      <c r="G181" s="49"/>
-      <c r="H181" s="49"/>
-      <c r="I181" s="49"/>
+      <c r="G181" s="51"/>
+      <c r="H181" s="51"/>
+      <c r="I181" s="51"/>
     </row>
     <row r="182" spans="2:9">
-      <c r="C182" s="48" t="s">
+      <c r="C182" s="52" t="s">
         <v>517</v>
       </c>
-      <c r="D182" s="48"/>
-      <c r="E182" s="48"/>
-      <c r="F182" s="49" t="s">
+      <c r="D182" s="52"/>
+      <c r="E182" s="52"/>
+      <c r="F182" s="51" t="s">
         <v>518</v>
       </c>
-      <c r="G182" s="49"/>
-      <c r="H182" s="49"/>
-      <c r="I182" s="49"/>
+      <c r="G182" s="51"/>
+      <c r="H182" s="51"/>
+      <c r="I182" s="51"/>
     </row>
     <row r="183" spans="2:9">
       <c r="B183" s="12"/>
@@ -14235,12 +14235,39 @@
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="D86:E86"/>
-    <mergeCell ref="D81:E81"/>
-    <mergeCell ref="D82:E82"/>
-    <mergeCell ref="D83:E83"/>
-    <mergeCell ref="D84:E84"/>
-    <mergeCell ref="D85:E85"/>
+    <mergeCell ref="F180:I180"/>
+    <mergeCell ref="F181:I181"/>
+    <mergeCell ref="F182:I182"/>
+    <mergeCell ref="C180:E180"/>
+    <mergeCell ref="C181:E181"/>
+    <mergeCell ref="C182:E182"/>
+    <mergeCell ref="C137:D137"/>
+    <mergeCell ref="C138:D138"/>
+    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="C140:D140"/>
+    <mergeCell ref="C141:D141"/>
+    <mergeCell ref="E137:I137"/>
+    <mergeCell ref="E138:I138"/>
+    <mergeCell ref="E139:I139"/>
+    <mergeCell ref="E140:I140"/>
+    <mergeCell ref="E141:I141"/>
+    <mergeCell ref="C131:D131"/>
+    <mergeCell ref="E126:I126"/>
+    <mergeCell ref="E127:I127"/>
+    <mergeCell ref="E128:I128"/>
+    <mergeCell ref="E129:I129"/>
+    <mergeCell ref="E130:I130"/>
+    <mergeCell ref="E131:I131"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="I87:J87"/>
+    <mergeCell ref="D105:G105"/>
+    <mergeCell ref="D106:G106"/>
+    <mergeCell ref="D107:G107"/>
+    <mergeCell ref="D108:G108"/>
     <mergeCell ref="E125:I125"/>
     <mergeCell ref="C125:D125"/>
     <mergeCell ref="I81:J81"/>
@@ -14257,39 +14284,12 @@
     <mergeCell ref="F85:H85"/>
     <mergeCell ref="F86:H86"/>
     <mergeCell ref="F87:H87"/>
-    <mergeCell ref="I87:J87"/>
-    <mergeCell ref="D105:G105"/>
-    <mergeCell ref="D106:G106"/>
-    <mergeCell ref="D107:G107"/>
-    <mergeCell ref="D108:G108"/>
-    <mergeCell ref="C131:D131"/>
-    <mergeCell ref="E126:I126"/>
-    <mergeCell ref="E127:I127"/>
-    <mergeCell ref="E128:I128"/>
-    <mergeCell ref="E129:I129"/>
-    <mergeCell ref="E130:I130"/>
-    <mergeCell ref="E131:I131"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="C127:D127"/>
-    <mergeCell ref="C128:D128"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="E137:I137"/>
-    <mergeCell ref="E138:I138"/>
-    <mergeCell ref="E139:I139"/>
-    <mergeCell ref="E140:I140"/>
-    <mergeCell ref="E141:I141"/>
-    <mergeCell ref="C137:D137"/>
-    <mergeCell ref="C138:D138"/>
-    <mergeCell ref="C139:D139"/>
-    <mergeCell ref="C140:D140"/>
-    <mergeCell ref="C141:D141"/>
-    <mergeCell ref="F180:I180"/>
-    <mergeCell ref="F181:I181"/>
-    <mergeCell ref="F182:I182"/>
-    <mergeCell ref="C180:E180"/>
-    <mergeCell ref="C181:E181"/>
-    <mergeCell ref="C182:E182"/>
+    <mergeCell ref="D86:E86"/>
+    <mergeCell ref="D81:E81"/>
+    <mergeCell ref="D82:E82"/>
+    <mergeCell ref="D83:E83"/>
+    <mergeCell ref="D84:E84"/>
+    <mergeCell ref="D85:E85"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -14828,7 +14828,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AA106"/>
+  <dimension ref="A1:AA96"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="3" max="3" width="12.3984375" customWidth="1"/>
@@ -14845,424 +14845,424 @@
       <c r="U6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="V6" s="50" t="s">
+      <c r="V6" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="W6" s="50"/>
-      <c r="X6" s="50"/>
-      <c r="Y6" s="50"/>
-      <c r="Z6" s="50"/>
-      <c r="AA6" s="50"/>
+      <c r="W6" s="53"/>
+      <c r="X6" s="53"/>
+      <c r="Y6" s="53"/>
+      <c r="Z6" s="53"/>
+      <c r="AA6" s="53"/>
     </row>
     <row r="7" spans="1:27">
       <c r="U7" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="V7" s="51" t="s">
+      <c r="V7" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="W7" s="51"/>
-      <c r="X7" s="51"/>
-      <c r="Y7" s="51"/>
-      <c r="Z7" s="51"/>
-      <c r="AA7" s="51"/>
+      <c r="W7" s="54"/>
+      <c r="X7" s="54"/>
+      <c r="Y7" s="54"/>
+      <c r="Z7" s="54"/>
+      <c r="AA7" s="54"/>
     </row>
     <row r="8" spans="1:27" ht="26.4">
       <c r="U8" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="V8" s="51" t="s">
+      <c r="V8" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="W8" s="51"/>
-      <c r="X8" s="51"/>
-      <c r="Y8" s="51"/>
-      <c r="Z8" s="51"/>
-      <c r="AA8" s="51"/>
+      <c r="W8" s="54"/>
+      <c r="X8" s="54"/>
+      <c r="Y8" s="54"/>
+      <c r="Z8" s="54"/>
+      <c r="AA8" s="54"/>
     </row>
     <row r="9" spans="1:27" ht="26.4">
       <c r="U9" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="V9" s="51" t="s">
+      <c r="V9" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="W9" s="51"/>
-      <c r="X9" s="51"/>
-      <c r="Y9" s="51"/>
-      <c r="Z9" s="51"/>
-      <c r="AA9" s="51"/>
-    </row>
-    <row r="36" spans="1:7" ht="22.8">
-      <c r="A36" s="5" t="s">
+      <c r="W9" s="54"/>
+      <c r="X9" s="54"/>
+      <c r="Y9" s="54"/>
+      <c r="Z9" s="54"/>
+      <c r="AA9" s="54"/>
+    </row>
+    <row r="27" spans="1:2" ht="22.8">
+      <c r="A27" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="12"/>
-      <c r="B37" s="12" t="s">
+    <row r="28" spans="1:2">
+      <c r="A28" s="12"/>
+      <c r="B28" s="12" t="s">
         <v>45</v>
       </c>
     </row>
+    <row r="29" spans="1:2">
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="22.8">
+      <c r="A32" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="22.8">
+      <c r="A35" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="17.399999999999999">
+      <c r="B37" s="14" t="s">
+        <v>52</v>
+      </c>
+    </row>
     <row r="38" spans="1:7">
-      <c r="B38" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="22.8">
-      <c r="A42" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="22.8">
-      <c r="A45" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="17.399999999999999">
-      <c r="B47" s="14" t="s">
-        <v>52</v>
+      <c r="B38" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" s="53"/>
+      <c r="D38" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53"/>
+    </row>
+    <row r="39" spans="1:7" ht="30.75" customHeight="1">
+      <c r="B39" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="51"/>
+      <c r="D39" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="E39" s="51"/>
+      <c r="F39" s="51"/>
+      <c r="G39" s="51"/>
+    </row>
+    <row r="40" spans="1:7" ht="30" customHeight="1">
+      <c r="B40" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="C40" s="51"/>
+      <c r="D40" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="E40" s="51"/>
+      <c r="F40" s="51"/>
+      <c r="G40" s="51"/>
+    </row>
+    <row r="41" spans="1:7" ht="31.5" customHeight="1">
+      <c r="B41" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" s="51"/>
+      <c r="D41" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="E41" s="51"/>
+      <c r="F41" s="51"/>
+      <c r="G41" s="51"/>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="B42" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="C42" s="51"/>
+      <c r="D42" s="62"/>
+      <c r="E42" s="62"/>
+      <c r="F42" s="62"/>
+      <c r="G42" s="62"/>
+    </row>
+    <row r="44" spans="1:7" ht="17.399999999999999">
+      <c r="A44" s="14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="B45" s="13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="B46" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="B47" s="13" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="48" spans="1:7">
-      <c r="B48" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="C48" s="50"/>
-      <c r="D48" s="50" t="s">
-        <v>54</v>
-      </c>
-      <c r="E48" s="50"/>
-      <c r="F48" s="50"/>
-      <c r="G48" s="50"/>
-    </row>
-    <row r="49" spans="1:7" ht="30.75" customHeight="1">
-      <c r="B49" s="49" t="s">
-        <v>55</v>
-      </c>
-      <c r="C49" s="49"/>
-      <c r="D49" s="49" t="s">
-        <v>56</v>
-      </c>
-      <c r="E49" s="49"/>
-      <c r="F49" s="49"/>
-      <c r="G49" s="49"/>
-    </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1">
-      <c r="B50" s="49" t="s">
-        <v>57</v>
-      </c>
-      <c r="C50" s="49"/>
-      <c r="D50" s="49" t="s">
-        <v>58</v>
-      </c>
-      <c r="E50" s="49"/>
-      <c r="F50" s="49"/>
-      <c r="G50" s="49"/>
-    </row>
-    <row r="51" spans="1:7" ht="31.5" customHeight="1">
-      <c r="B51" s="49" t="s">
-        <v>59</v>
-      </c>
-      <c r="C51" s="49"/>
-      <c r="D51" s="49" t="s">
-        <v>60</v>
-      </c>
-      <c r="E51" s="49"/>
-      <c r="F51" s="49"/>
-      <c r="G51" s="49"/>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="B52" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="C52" s="49"/>
-      <c r="D52" s="59"/>
-      <c r="E52" s="59"/>
-      <c r="F52" s="59"/>
-      <c r="G52" s="59"/>
-    </row>
-    <row r="54" spans="1:7" ht="17.399999999999999">
-      <c r="A54" s="14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="B55" s="13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+      <c r="B48" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="B49" s="11"/>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="B50" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="B51" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="B52" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="B53" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
       <c r="B56" s="13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
       <c r="B57" s="13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
       <c r="B58" s="13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="B59" s="11"/>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="B60" s="13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="B61" s="13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="B62" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="B63" s="13" t="s">
-        <v>67</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="B59" s="13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="22.8">
+      <c r="A61" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="12"/>
+      <c r="B62" s="12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="B63" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="B64" s="16" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="7" t="s">
-        <v>71</v>
+      <c r="B65" s="16" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="B66" s="13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="B67" s="13" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="B68" s="13" t="s">
-        <v>73</v>
+      <c r="B66" s="15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="17.399999999999999">
+      <c r="A68" s="14" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="B69" s="13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" ht="22.8">
-      <c r="A71" s="5" t="s">
-        <v>75</v>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="B70" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="B71" s="13" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="12"/>
-      <c r="B72" s="12" t="s">
-        <v>76</v>
+      <c r="B72" s="13" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="B73" s="12" t="s">
-        <v>77</v>
+      <c r="B73" s="13" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="B74" s="16" t="s">
-        <v>78</v>
+      <c r="B74" s="13" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="B75" s="16" t="s">
-        <v>79</v>
+      <c r="B75" s="13" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="B76" s="15" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" ht="17.399999999999999">
-      <c r="A78" s="14" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
-      <c r="B79" s="13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="B80" s="13" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
-      <c r="B81" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="B82" s="13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
-      <c r="B83" s="13" t="s">
+      <c r="B76" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="B77" s="13" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
-      <c r="B84" s="13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
-      <c r="B85" s="13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
-      <c r="B86" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
+    <row r="79" spans="1:2" ht="22.8">
+      <c r="A79" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="B83" s="12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="B84" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="B85" s="12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
       <c r="B87" s="13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" ht="22.8">
-      <c r="A89" s="5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
-      <c r="B91" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
-      <c r="B92" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
-      <c r="B93" s="12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
-      <c r="B94" s="12" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
-      <c r="B95" s="12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
-      <c r="B96" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="13" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
-      <c r="B99" s="8" t="s">
+    <row r="89" spans="1:6">
+      <c r="B89" s="8" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
-      <c r="B100" s="8"/>
-    </row>
-    <row r="101" spans="1:6" ht="22.8">
-      <c r="A101" s="5" t="s">
+    <row r="90" spans="1:6">
+      <c r="B90" s="8"/>
+    </row>
+    <row r="91" spans="1:6" ht="22.8">
+      <c r="A91" s="5" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="27.6">
-      <c r="B103" s="1" t="s">
+    <row r="93" spans="1:6" ht="27.6">
+      <c r="B93" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C103" s="50" t="s">
+      <c r="C93" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="D103" s="50"/>
-      <c r="E103" s="50"/>
-      <c r="F103" s="50"/>
-    </row>
-    <row r="104" spans="1:6" ht="27">
-      <c r="B104" s="2" t="s">
+      <c r="D93" s="53"/>
+      <c r="E93" s="53"/>
+      <c r="F93" s="53"/>
+    </row>
+    <row r="94" spans="1:6" ht="27">
+      <c r="B94" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C104" s="48" t="s">
+      <c r="C94" s="52" t="s">
         <v>95</v>
       </c>
-      <c r="D104" s="48"/>
-      <c r="E104" s="48"/>
-      <c r="F104" s="48"/>
-    </row>
-    <row r="105" spans="1:6" ht="27">
-      <c r="B105" s="2" t="s">
+      <c r="D94" s="52"/>
+      <c r="E94" s="52"/>
+      <c r="F94" s="52"/>
+    </row>
+    <row r="95" spans="1:6" ht="27">
+      <c r="B95" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C105" s="49" t="s">
+      <c r="C95" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="D105" s="49"/>
-      <c r="E105" s="49"/>
-      <c r="F105" s="49"/>
-    </row>
-    <row r="106" spans="1:6" ht="27">
-      <c r="B106" s="2" t="s">
+      <c r="D95" s="51"/>
+      <c r="E95" s="51"/>
+      <c r="F95" s="51"/>
+    </row>
+    <row r="96" spans="1:6" ht="27">
+      <c r="B96" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C106" s="48" t="s">
+      <c r="C96" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="D106" s="48"/>
-      <c r="E106" s="48"/>
-      <c r="F106" s="48"/>
+      <c r="D96" s="52"/>
+      <c r="E96" s="52"/>
+      <c r="F96" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="C95:F95"/>
+    <mergeCell ref="C96:F96"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D40:G40"/>
+    <mergeCell ref="D41:G41"/>
+    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="C93:F93"/>
+    <mergeCell ref="C94:F94"/>
+    <mergeCell ref="B39:C39"/>
     <mergeCell ref="V6:AA6"/>
     <mergeCell ref="V7:AA7"/>
     <mergeCell ref="V8:AA8"/>
     <mergeCell ref="V9:AA9"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="D48:G48"/>
-    <mergeCell ref="D49:G49"/>
-    <mergeCell ref="D50:G50"/>
-    <mergeCell ref="D51:G51"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="C103:F103"/>
-    <mergeCell ref="C104:F104"/>
-    <mergeCell ref="C105:F105"/>
-    <mergeCell ref="C106:F106"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:G38"/>
+    <mergeCell ref="D39:G39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -15317,79 +15317,79 @@
       </c>
     </row>
     <row r="12" spans="2:10">
-      <c r="B12" s="50" t="s">
+      <c r="B12" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50" t="s">
+      <c r="C12" s="53"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53" t="s">
         <v>217</v>
       </c>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
     </row>
     <row r="13" spans="2:10">
-      <c r="B13" s="49" t="s">
+      <c r="B13" s="51" t="s">
         <v>218</v>
       </c>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49" t="s">
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51" t="s">
         <v>219</v>
       </c>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="49"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
     </row>
     <row r="14" spans="2:10">
-      <c r="B14" s="49" t="s">
+      <c r="B14" s="51" t="s">
         <v>220</v>
       </c>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49" t="s">
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51" t="s">
         <v>221</v>
       </c>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="49"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51"/>
     </row>
     <row r="15" spans="2:10">
-      <c r="B15" s="49" t="s">
+      <c r="B15" s="51" t="s">
         <v>222</v>
       </c>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49" t="s">
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51" t="s">
         <v>223</v>
       </c>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="49"/>
-      <c r="J15" s="49"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
     </row>
     <row r="16" spans="2:10">
-      <c r="B16" s="49" t="s">
+      <c r="B16" s="51" t="s">
         <v>224</v>
       </c>
-      <c r="C16" s="49"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49" t="s">
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51" t="s">
         <v>225</v>
       </c>
-      <c r="F16" s="49"/>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49"/>
-      <c r="I16" s="49"/>
-      <c r="J16" s="49"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
     </row>
     <row r="19" spans="2:12">
       <c r="B19" t="s">
@@ -15400,115 +15400,115 @@
       <c r="B21" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C21" s="50" t="s">
+      <c r="C21" s="53" t="s">
         <v>192</v>
       </c>
-      <c r="D21" s="50"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="50" t="s">
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="J21" s="50"/>
-      <c r="K21" s="50"/>
-      <c r="L21" s="50"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="53"/>
     </row>
     <row r="22" spans="2:12" ht="27.6">
       <c r="B22" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C22" s="49" t="s">
+      <c r="C22" s="51" t="s">
         <v>195</v>
       </c>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="49" t="s">
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51" t="s">
         <v>196</v>
       </c>
-      <c r="J22" s="49"/>
-      <c r="K22" s="49"/>
-      <c r="L22" s="49"/>
+      <c r="J22" s="51"/>
+      <c r="K22" s="51"/>
+      <c r="L22" s="51"/>
     </row>
     <row r="23" spans="2:12" ht="27.6">
       <c r="B23" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C23" s="49" t="s">
+      <c r="C23" s="51" t="s">
         <v>198</v>
       </c>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="49" t="s">
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="51" t="s">
         <v>199</v>
       </c>
-      <c r="J23" s="49"/>
-      <c r="K23" s="49"/>
-      <c r="L23" s="49"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="51"/>
+      <c r="L23" s="51"/>
     </row>
     <row r="24" spans="2:12" ht="27.6">
       <c r="B24" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C24" s="49" t="s">
+      <c r="C24" s="51" t="s">
         <v>201</v>
       </c>
-      <c r="D24" s="49"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="49" t="s">
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="51" t="s">
         <v>202</v>
       </c>
-      <c r="J24" s="49"/>
-      <c r="K24" s="49"/>
-      <c r="L24" s="49"/>
+      <c r="J24" s="51"/>
+      <c r="K24" s="51"/>
+      <c r="L24" s="51"/>
     </row>
     <row r="25" spans="2:12">
       <c r="B25" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C25" s="49" t="s">
+      <c r="C25" s="51" t="s">
         <v>204</v>
       </c>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="49"/>
-      <c r="I25" s="49" t="s">
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="51" t="s">
         <v>205</v>
       </c>
-      <c r="J25" s="49"/>
-      <c r="K25" s="49"/>
-      <c r="L25" s="49"/>
+      <c r="J25" s="51"/>
+      <c r="K25" s="51"/>
+      <c r="L25" s="51"/>
     </row>
     <row r="26" spans="2:12">
       <c r="B26" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C26" s="49" t="s">
+      <c r="C26" s="51" t="s">
         <v>207</v>
       </c>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49" t="s">
+      <c r="D26" s="51"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="51"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="51"/>
+      <c r="I26" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="J26" s="49"/>
-      <c r="K26" s="49"/>
-      <c r="L26" s="49"/>
+      <c r="J26" s="51"/>
+      <c r="K26" s="51"/>
+      <c r="L26" s="51"/>
     </row>
     <row r="29" spans="2:12" ht="17.399999999999999">
       <c r="B29" s="14" t="s">
@@ -15705,6 +15705,16 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="E12:J12"/>
+    <mergeCell ref="E13:J13"/>
+    <mergeCell ref="E14:J14"/>
+    <mergeCell ref="E15:J15"/>
+    <mergeCell ref="E16:J16"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
     <mergeCell ref="I26:L26"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="C22:H22"/>
@@ -15717,16 +15727,6 @@
     <mergeCell ref="I23:L23"/>
     <mergeCell ref="I24:L24"/>
     <mergeCell ref="I25:L25"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E12:J12"/>
-    <mergeCell ref="E13:J13"/>
-    <mergeCell ref="E14:J14"/>
-    <mergeCell ref="E15:J15"/>
-    <mergeCell ref="E16:J16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -15770,76 +15770,76 @@
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="B9" s="50" t="s">
+      <c r="B9" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="50"/>
-      <c r="D9" s="50" t="s">
+      <c r="C9" s="53"/>
+      <c r="D9" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
     </row>
     <row r="10" spans="1:7" ht="32.25" customHeight="1">
-      <c r="B10" s="51" t="s">
+      <c r="B10" s="54" t="s">
         <v>528</v>
       </c>
-      <c r="C10" s="51"/>
-      <c r="D10" s="49" t="s">
+      <c r="C10" s="54"/>
+      <c r="D10" s="51" t="s">
         <v>529</v>
       </c>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
     </row>
     <row r="11" spans="1:7" ht="30" customHeight="1">
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="54" t="s">
         <v>530</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="49" t="s">
+      <c r="C11" s="54"/>
+      <c r="D11" s="51" t="s">
         <v>531</v>
       </c>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="54" t="s">
         <v>532</v>
       </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="49" t="s">
+      <c r="C12" s="54"/>
+      <c r="D12" s="51" t="s">
         <v>533</v>
       </c>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
     </row>
     <row r="13" spans="1:7" ht="30.75" customHeight="1">
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="54" t="s">
         <v>534</v>
       </c>
-      <c r="C13" s="51"/>
-      <c r="D13" s="49" t="s">
+      <c r="C13" s="54"/>
+      <c r="D13" s="51" t="s">
         <v>535</v>
       </c>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
     </row>
     <row r="14" spans="1:7" ht="34.5" customHeight="1">
-      <c r="B14" s="51" t="s">
+      <c r="B14" s="54" t="s">
         <v>536</v>
       </c>
-      <c r="C14" s="51"/>
-      <c r="D14" s="49" t="s">
+      <c r="C14" s="54"/>
+      <c r="D14" s="51" t="s">
         <v>537</v>
       </c>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
     </row>
     <row r="16" spans="1:7" ht="30">
       <c r="A16" s="32" t="s">
@@ -16048,268 +16048,268 @@
       <c r="A5" s="32" t="s">
         <v>573</v>
       </c>
-      <c r="P5" s="50" t="s">
+      <c r="P5" s="53" t="s">
         <v>637</v>
       </c>
-      <c r="Q5" s="50"/>
-      <c r="R5" s="50" t="s">
+      <c r="Q5" s="53"/>
+      <c r="R5" s="53" t="s">
         <v>638</v>
       </c>
-      <c r="S5" s="50"/>
-      <c r="T5" s="50"/>
-      <c r="U5" s="50" t="s">
+      <c r="S5" s="53"/>
+      <c r="T5" s="53"/>
+      <c r="U5" s="53" t="s">
         <v>574</v>
       </c>
-      <c r="V5" s="50"/>
-      <c r="W5" s="50"/>
-      <c r="X5" s="50"/>
-      <c r="Y5" s="50"/>
+      <c r="V5" s="53"/>
+      <c r="W5" s="53"/>
+      <c r="X5" s="53"/>
+      <c r="Y5" s="53"/>
     </row>
     <row r="6" spans="1:25">
-      <c r="P6" s="51" t="s">
+      <c r="P6" s="54" t="s">
         <v>639</v>
       </c>
-      <c r="Q6" s="51"/>
-      <c r="R6" s="48" t="s">
+      <c r="Q6" s="54"/>
+      <c r="R6" s="52" t="s">
         <v>640</v>
       </c>
-      <c r="S6" s="48"/>
-      <c r="T6" s="48"/>
-      <c r="U6" s="49" t="s">
+      <c r="S6" s="52"/>
+      <c r="T6" s="52"/>
+      <c r="U6" s="51" t="s">
         <v>641</v>
       </c>
-      <c r="V6" s="49"/>
-      <c r="W6" s="49"/>
-      <c r="X6" s="49"/>
-      <c r="Y6" s="49"/>
+      <c r="V6" s="51"/>
+      <c r="W6" s="51"/>
+      <c r="X6" s="51"/>
+      <c r="Y6" s="51"/>
     </row>
     <row r="7" spans="1:25">
-      <c r="B7" s="50" t="s">
+      <c r="B7" s="53" t="s">
         <v>170</v>
       </c>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50" t="s">
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53" t="s">
         <v>574</v>
       </c>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="50"/>
-      <c r="P7" s="51" t="s">
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="P7" s="54" t="s">
         <v>642</v>
       </c>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="48" t="s">
+      <c r="Q7" s="54"/>
+      <c r="R7" s="52" t="s">
         <v>643</v>
       </c>
-      <c r="S7" s="48"/>
-      <c r="T7" s="48"/>
-      <c r="U7" s="49" t="s">
+      <c r="S7" s="52"/>
+      <c r="T7" s="52"/>
+      <c r="U7" s="51" t="s">
         <v>644</v>
       </c>
-      <c r="V7" s="49"/>
-      <c r="W7" s="49"/>
-      <c r="X7" s="49"/>
-      <c r="Y7" s="49"/>
+      <c r="V7" s="51"/>
+      <c r="W7" s="51"/>
+      <c r="X7" s="51"/>
+      <c r="Y7" s="51"/>
     </row>
     <row r="8" spans="1:25">
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="54" t="s">
         <v>575</v>
       </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="49" t="s">
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="51" t="s">
         <v>576</v>
       </c>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="P8" s="51" t="s">
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="P8" s="54" t="s">
         <v>645</v>
       </c>
-      <c r="Q8" s="51"/>
-      <c r="R8" s="48" t="s">
+      <c r="Q8" s="54"/>
+      <c r="R8" s="52" t="s">
         <v>646</v>
       </c>
-      <c r="S8" s="48"/>
-      <c r="T8" s="48"/>
-      <c r="U8" s="49" t="s">
+      <c r="S8" s="52"/>
+      <c r="T8" s="52"/>
+      <c r="U8" s="51" t="s">
         <v>647</v>
       </c>
-      <c r="V8" s="49"/>
-      <c r="W8" s="49"/>
-      <c r="X8" s="49"/>
-      <c r="Y8" s="49"/>
+      <c r="V8" s="51"/>
+      <c r="W8" s="51"/>
+      <c r="X8" s="51"/>
+      <c r="Y8" s="51"/>
     </row>
     <row r="9" spans="1:25">
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="54" t="s">
         <v>577</v>
       </c>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="49" t="s">
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="51" t="s">
         <v>578</v>
       </c>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="P9" s="51" t="s">
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="P9" s="54" t="s">
         <v>648</v>
       </c>
-      <c r="Q9" s="51"/>
-      <c r="R9" s="48" t="s">
+      <c r="Q9" s="54"/>
+      <c r="R9" s="52" t="s">
         <v>649</v>
       </c>
-      <c r="S9" s="48"/>
-      <c r="T9" s="48"/>
-      <c r="U9" s="49" t="s">
+      <c r="S9" s="52"/>
+      <c r="T9" s="52"/>
+      <c r="U9" s="51" t="s">
         <v>650</v>
       </c>
-      <c r="V9" s="49"/>
-      <c r="W9" s="49"/>
-      <c r="X9" s="49"/>
-      <c r="Y9" s="49"/>
+      <c r="V9" s="51"/>
+      <c r="W9" s="51"/>
+      <c r="X9" s="51"/>
+      <c r="Y9" s="51"/>
     </row>
     <row r="10" spans="1:25">
-      <c r="B10" s="51" t="s">
+      <c r="B10" s="54" t="s">
         <v>579</v>
       </c>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="49" t="s">
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="51" t="s">
         <v>580</v>
       </c>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="P10" s="51" t="s">
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="P10" s="54" t="s">
         <v>651</v>
       </c>
-      <c r="Q10" s="51"/>
-      <c r="R10" s="48" t="s">
+      <c r="Q10" s="54"/>
+      <c r="R10" s="52" t="s">
         <v>652</v>
       </c>
-      <c r="S10" s="48"/>
-      <c r="T10" s="48"/>
-      <c r="U10" s="49" t="s">
+      <c r="S10" s="52"/>
+      <c r="T10" s="52"/>
+      <c r="U10" s="51" t="s">
         <v>653</v>
       </c>
-      <c r="V10" s="49"/>
-      <c r="W10" s="49"/>
-      <c r="X10" s="49"/>
-      <c r="Y10" s="49"/>
+      <c r="V10" s="51"/>
+      <c r="W10" s="51"/>
+      <c r="X10" s="51"/>
+      <c r="Y10" s="51"/>
     </row>
     <row r="11" spans="1:25">
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="54" t="s">
         <v>581</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="49" t="s">
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="51" t="s">
         <v>582</v>
       </c>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="49"/>
-      <c r="P11" s="51" t="s">
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="P11" s="54" t="s">
         <v>654</v>
       </c>
-      <c r="Q11" s="51"/>
-      <c r="R11" s="48" t="s">
+      <c r="Q11" s="54"/>
+      <c r="R11" s="52" t="s">
         <v>655</v>
       </c>
-      <c r="S11" s="48"/>
-      <c r="T11" s="48"/>
-      <c r="U11" s="49" t="s">
+      <c r="S11" s="52"/>
+      <c r="T11" s="52"/>
+      <c r="U11" s="51" t="s">
         <v>656</v>
       </c>
-      <c r="V11" s="49"/>
-      <c r="W11" s="49"/>
-      <c r="X11" s="49"/>
-      <c r="Y11" s="49"/>
+      <c r="V11" s="51"/>
+      <c r="W11" s="51"/>
+      <c r="X11" s="51"/>
+      <c r="Y11" s="51"/>
     </row>
     <row r="12" spans="1:25">
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="54" t="s">
         <v>583</v>
       </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="49" t="s">
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="51" t="s">
         <v>584</v>
       </c>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="49"/>
-      <c r="P12" s="51" t="s">
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="P12" s="54" t="s">
         <v>657</v>
       </c>
-      <c r="Q12" s="51"/>
-      <c r="R12" s="48" t="s">
+      <c r="Q12" s="54"/>
+      <c r="R12" s="52" t="s">
         <v>658</v>
       </c>
-      <c r="S12" s="48"/>
-      <c r="T12" s="48"/>
-      <c r="U12" s="49" t="s">
+      <c r="S12" s="52"/>
+      <c r="T12" s="52"/>
+      <c r="U12" s="51" t="s">
         <v>659</v>
       </c>
-      <c r="V12" s="49"/>
-      <c r="W12" s="49"/>
-      <c r="X12" s="49"/>
-      <c r="Y12" s="49"/>
+      <c r="V12" s="51"/>
+      <c r="W12" s="51"/>
+      <c r="X12" s="51"/>
+      <c r="Y12" s="51"/>
     </row>
     <row r="13" spans="1:25">
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="54" t="s">
         <v>585</v>
       </c>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="49" t="s">
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="51" t="s">
         <v>586</v>
       </c>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="49"/>
-      <c r="P13" s="51" t="s">
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="P13" s="54" t="s">
         <v>660</v>
       </c>
-      <c r="Q13" s="51"/>
-      <c r="R13" s="48" t="s">
+      <c r="Q13" s="54"/>
+      <c r="R13" s="52" t="s">
         <v>661</v>
       </c>
-      <c r="S13" s="48"/>
-      <c r="T13" s="48"/>
-      <c r="U13" s="49" t="s">
+      <c r="S13" s="52"/>
+      <c r="T13" s="52"/>
+      <c r="U13" s="51" t="s">
         <v>662</v>
       </c>
-      <c r="V13" s="49"/>
-      <c r="W13" s="49"/>
-      <c r="X13" s="49"/>
-      <c r="Y13" s="49"/>
+      <c r="V13" s="51"/>
+      <c r="W13" s="51"/>
+      <c r="X13" s="51"/>
+      <c r="Y13" s="51"/>
     </row>
     <row r="14" spans="1:25">
-      <c r="P14" s="51" t="s">
+      <c r="P14" s="54" t="s">
         <v>663</v>
       </c>
-      <c r="Q14" s="51"/>
-      <c r="R14" s="48" t="s">
+      <c r="Q14" s="54"/>
+      <c r="R14" s="52" t="s">
         <v>664</v>
       </c>
-      <c r="S14" s="48"/>
-      <c r="T14" s="48"/>
-      <c r="U14" s="49" t="s">
+      <c r="S14" s="52"/>
+      <c r="T14" s="52"/>
+      <c r="U14" s="51" t="s">
         <v>665</v>
       </c>
-      <c r="V14" s="49"/>
-      <c r="W14" s="49"/>
-      <c r="X14" s="49"/>
-      <c r="Y14" s="49"/>
+      <c r="V14" s="51"/>
+      <c r="W14" s="51"/>
+      <c r="X14" s="51"/>
+      <c r="Y14" s="51"/>
     </row>
     <row r="16" spans="1:25" ht="30">
       <c r="A16" s="32" t="s">
@@ -16442,102 +16442,102 @@
       </c>
     </row>
     <row r="45" spans="1:9">
-      <c r="B45" s="50" t="s">
+      <c r="B45" s="53" t="s">
         <v>613</v>
       </c>
-      <c r="C45" s="50"/>
-      <c r="D45" s="50"/>
-      <c r="E45" s="50" t="s">
+      <c r="C45" s="53"/>
+      <c r="D45" s="53"/>
+      <c r="E45" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="F45" s="50"/>
-      <c r="G45" s="50"/>
-      <c r="H45" s="50"/>
-      <c r="I45" s="50"/>
+      <c r="F45" s="53"/>
+      <c r="G45" s="53"/>
+      <c r="H45" s="53"/>
+      <c r="I45" s="53"/>
     </row>
     <row r="46" spans="1:9">
-      <c r="B46" s="48" t="s">
+      <c r="B46" s="52" t="s">
         <v>614</v>
       </c>
-      <c r="C46" s="48"/>
-      <c r="D46" s="48"/>
-      <c r="E46" s="49" t="s">
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="51" t="s">
         <v>615</v>
       </c>
-      <c r="F46" s="49"/>
-      <c r="G46" s="49"/>
-      <c r="H46" s="49"/>
-      <c r="I46" s="49"/>
+      <c r="F46" s="51"/>
+      <c r="G46" s="51"/>
+      <c r="H46" s="51"/>
+      <c r="I46" s="51"/>
     </row>
     <row r="47" spans="1:9">
-      <c r="B47" s="48" t="s">
+      <c r="B47" s="52" t="s">
         <v>616</v>
       </c>
-      <c r="C47" s="48"/>
-      <c r="D47" s="48"/>
-      <c r="E47" s="49" t="s">
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="51" t="s">
         <v>617</v>
       </c>
-      <c r="F47" s="49"/>
-      <c r="G47" s="49"/>
-      <c r="H47" s="49"/>
-      <c r="I47" s="49"/>
+      <c r="F47" s="51"/>
+      <c r="G47" s="51"/>
+      <c r="H47" s="51"/>
+      <c r="I47" s="51"/>
     </row>
     <row r="48" spans="1:9">
-      <c r="B48" s="48" t="s">
+      <c r="B48" s="52" t="s">
         <v>618</v>
       </c>
-      <c r="C48" s="48"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="49" t="s">
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="51" t="s">
         <v>619</v>
       </c>
-      <c r="F48" s="49"/>
-      <c r="G48" s="49"/>
-      <c r="H48" s="49"/>
-      <c r="I48" s="49"/>
+      <c r="F48" s="51"/>
+      <c r="G48" s="51"/>
+      <c r="H48" s="51"/>
+      <c r="I48" s="51"/>
     </row>
     <row r="49" spans="1:9">
-      <c r="B49" s="48" t="s">
+      <c r="B49" s="52" t="s">
         <v>620</v>
       </c>
-      <c r="C49" s="48"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="49" t="s">
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="51" t="s">
         <v>621</v>
       </c>
-      <c r="F49" s="49"/>
-      <c r="G49" s="49"/>
-      <c r="H49" s="49"/>
-      <c r="I49" s="49"/>
+      <c r="F49" s="51"/>
+      <c r="G49" s="51"/>
+      <c r="H49" s="51"/>
+      <c r="I49" s="51"/>
     </row>
     <row r="50" spans="1:9">
-      <c r="B50" s="48" t="s">
+      <c r="B50" s="52" t="s">
         <v>622</v>
       </c>
-      <c r="C50" s="48"/>
-      <c r="D50" s="48"/>
-      <c r="E50" s="49" t="s">
+      <c r="C50" s="52"/>
+      <c r="D50" s="52"/>
+      <c r="E50" s="51" t="s">
         <v>623</v>
       </c>
-      <c r="F50" s="49"/>
-      <c r="G50" s="49"/>
-      <c r="H50" s="49"/>
-      <c r="I50" s="49"/>
+      <c r="F50" s="51"/>
+      <c r="G50" s="51"/>
+      <c r="H50" s="51"/>
+      <c r="I50" s="51"/>
     </row>
     <row r="51" spans="1:9" ht="32.25" customHeight="1">
-      <c r="B51" s="48" t="s">
+      <c r="B51" s="52" t="s">
         <v>624</v>
       </c>
-      <c r="C51" s="48"/>
-      <c r="D51" s="48"/>
-      <c r="E51" s="49" t="s">
+      <c r="C51" s="52"/>
+      <c r="D51" s="52"/>
+      <c r="E51" s="51" t="s">
         <v>625</v>
       </c>
-      <c r="F51" s="49"/>
-      <c r="G51" s="49"/>
-      <c r="H51" s="49"/>
-      <c r="I51" s="49"/>
+      <c r="F51" s="51"/>
+      <c r="G51" s="51"/>
+      <c r="H51" s="51"/>
+      <c r="I51" s="51"/>
     </row>
     <row r="54" spans="1:9" ht="30">
       <c r="A54" s="32" t="s">
@@ -16545,109 +16545,97 @@
       </c>
     </row>
     <row r="56" spans="1:9">
-      <c r="B56" s="50" t="s">
+      <c r="B56" s="53" t="s">
         <v>627</v>
       </c>
-      <c r="C56" s="50"/>
-      <c r="D56" s="50"/>
-      <c r="E56" s="50" t="s">
+      <c r="C56" s="53"/>
+      <c r="D56" s="53"/>
+      <c r="E56" s="53" t="s">
         <v>628</v>
       </c>
-      <c r="F56" s="50"/>
-      <c r="G56" s="50"/>
-      <c r="H56" s="50"/>
-      <c r="I56" s="50"/>
+      <c r="F56" s="53"/>
+      <c r="G56" s="53"/>
+      <c r="H56" s="53"/>
+      <c r="I56" s="53"/>
     </row>
     <row r="57" spans="1:9" ht="33.75" customHeight="1">
-      <c r="B57" s="49" t="s">
+      <c r="B57" s="51" t="s">
         <v>629</v>
       </c>
-      <c r="C57" s="49"/>
-      <c r="D57" s="49"/>
-      <c r="E57" s="49" t="s">
+      <c r="C57" s="51"/>
+      <c r="D57" s="51"/>
+      <c r="E57" s="51" t="s">
         <v>630</v>
       </c>
-      <c r="F57" s="49"/>
-      <c r="G57" s="49"/>
-      <c r="H57" s="49"/>
-      <c r="I57" s="49"/>
+      <c r="F57" s="51"/>
+      <c r="G57" s="51"/>
+      <c r="H57" s="51"/>
+      <c r="I57" s="51"/>
     </row>
     <row r="58" spans="1:9">
-      <c r="B58" s="49" t="s">
+      <c r="B58" s="51" t="s">
         <v>631</v>
       </c>
-      <c r="C58" s="49"/>
-      <c r="D58" s="49"/>
-      <c r="E58" s="49" t="s">
+      <c r="C58" s="51"/>
+      <c r="D58" s="51"/>
+      <c r="E58" s="51" t="s">
         <v>632</v>
       </c>
-      <c r="F58" s="49"/>
-      <c r="G58" s="49"/>
-      <c r="H58" s="49"/>
-      <c r="I58" s="49"/>
+      <c r="F58" s="51"/>
+      <c r="G58" s="51"/>
+      <c r="H58" s="51"/>
+      <c r="I58" s="51"/>
     </row>
     <row r="59" spans="1:9">
-      <c r="B59" s="49" t="s">
+      <c r="B59" s="51" t="s">
         <v>633</v>
       </c>
-      <c r="C59" s="49"/>
-      <c r="D59" s="49"/>
-      <c r="E59" s="49" t="s">
+      <c r="C59" s="51"/>
+      <c r="D59" s="51"/>
+      <c r="E59" s="51" t="s">
         <v>634</v>
       </c>
-      <c r="F59" s="49"/>
-      <c r="G59" s="49"/>
-      <c r="H59" s="49"/>
-      <c r="I59" s="49"/>
+      <c r="F59" s="51"/>
+      <c r="G59" s="51"/>
+      <c r="H59" s="51"/>
+      <c r="I59" s="51"/>
     </row>
     <row r="60" spans="1:9" ht="30.75" customHeight="1">
-      <c r="B60" s="49" t="s">
+      <c r="B60" s="51" t="s">
         <v>635</v>
       </c>
-      <c r="C60" s="49"/>
-      <c r="D60" s="49"/>
-      <c r="E60" s="49" t="s">
+      <c r="C60" s="51"/>
+      <c r="D60" s="51"/>
+      <c r="E60" s="51" t="s">
         <v>636</v>
       </c>
-      <c r="F60" s="49"/>
-      <c r="G60" s="49"/>
-      <c r="H60" s="49"/>
-      <c r="I60" s="49"/>
+      <c r="F60" s="51"/>
+      <c r="G60" s="51"/>
+      <c r="H60" s="51"/>
+      <c r="I60" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="E7:I7"/>
-    <mergeCell ref="E8:I8"/>
-    <mergeCell ref="E9:I9"/>
-    <mergeCell ref="E10:I10"/>
-    <mergeCell ref="E11:I11"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="R5:T5"/>
-    <mergeCell ref="R6:T6"/>
-    <mergeCell ref="R7:T7"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="R9:T9"/>
-    <mergeCell ref="U10:Y10"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="R10:T10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="U5:Y5"/>
-    <mergeCell ref="U6:Y6"/>
-    <mergeCell ref="U7:Y7"/>
-    <mergeCell ref="U8:Y8"/>
-    <mergeCell ref="U9:Y9"/>
+    <mergeCell ref="E57:I57"/>
+    <mergeCell ref="E58:I58"/>
+    <mergeCell ref="E60:I60"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="E59:I59"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="E50:I50"/>
+    <mergeCell ref="E51:I51"/>
+    <mergeCell ref="E56:I56"/>
+    <mergeCell ref="E47:I47"/>
+    <mergeCell ref="E48:I48"/>
+    <mergeCell ref="E49:I49"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B49:D49"/>
     <mergeCell ref="B46:D46"/>
     <mergeCell ref="R11:T11"/>
     <mergeCell ref="R12:T12"/>
@@ -16657,33 +16645,45 @@
     <mergeCell ref="E12:I12"/>
     <mergeCell ref="E13:I13"/>
     <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="E45:I45"/>
+    <mergeCell ref="E46:I46"/>
+    <mergeCell ref="U5:Y5"/>
+    <mergeCell ref="U6:Y6"/>
+    <mergeCell ref="U7:Y7"/>
+    <mergeCell ref="U8:Y8"/>
+    <mergeCell ref="U9:Y9"/>
+    <mergeCell ref="U10:Y10"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="R10:T10"/>
+    <mergeCell ref="P10:Q10"/>
     <mergeCell ref="U11:Y11"/>
     <mergeCell ref="U12:Y12"/>
     <mergeCell ref="U13:Y13"/>
     <mergeCell ref="U14:Y14"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="E45:I45"/>
-    <mergeCell ref="E46:I46"/>
-    <mergeCell ref="E47:I47"/>
-    <mergeCell ref="E48:I48"/>
-    <mergeCell ref="E49:I49"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="E50:I50"/>
-    <mergeCell ref="E51:I51"/>
-    <mergeCell ref="E56:I56"/>
-    <mergeCell ref="E57:I57"/>
-    <mergeCell ref="E58:I58"/>
-    <mergeCell ref="E60:I60"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="E59:I59"/>
+    <mergeCell ref="R5:T5"/>
+    <mergeCell ref="R6:T6"/>
+    <mergeCell ref="R7:T7"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="R9:T9"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="E7:I7"/>
+    <mergeCell ref="E8:I8"/>
+    <mergeCell ref="E9:I9"/>
+    <mergeCell ref="E10:I10"/>
+    <mergeCell ref="E11:I11"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
